--- a/Trabalho_2/dados/normal/quartoteste_helicenormal.xlsx
+++ b/Trabalho_2/dados/normal/quartoteste_helicenormal.xlsx
@@ -3952,11 +3952,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="67393524"/>
-        <c:axId val="95638489"/>
+        <c:axId val="68167828"/>
+        <c:axId val="20343728"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67393524"/>
+        <c:axId val="68167828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4022,7 +4022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95638489"/>
+        <c:crossAx val="20343728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4030,7 +4030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95638489"/>
+        <c:axId val="20343728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4106,7 +4106,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67393524"/>
+        <c:crossAx val="68167828"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7880,11 +7880,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47310763"/>
-        <c:axId val="85529971"/>
+        <c:axId val="33888171"/>
+        <c:axId val="74185603"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47310763"/>
+        <c:axId val="33888171"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7950,7 +7950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85529971"/>
+        <c:crossAx val="74185603"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7958,7 +7958,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85529971"/>
+        <c:axId val="74185603"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8034,7 +8034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47310763"/>
+        <c:crossAx val="33888171"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11808,11 +11808,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54389601"/>
-        <c:axId val="92521566"/>
+        <c:axId val="96582138"/>
+        <c:axId val="44841253"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54389601"/>
+        <c:axId val="96582138"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11878,7 +11878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92521566"/>
+        <c:crossAx val="44841253"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11886,7 +11886,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92521566"/>
+        <c:axId val="44841253"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11962,7 +11962,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54389601"/>
+        <c:crossAx val="96582138"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12682,9 +12682,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>302040</xdr:colOff>
+      <xdr:colOff>301680</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>73440</xdr:rowOff>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12693,7 +12693,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="190440"/>
-        <a:ext cx="4515840" cy="2740680"/>
+        <a:ext cx="4515480" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12712,9 +12712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>302040</xdr:colOff>
+      <xdr:colOff>301680</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>73440</xdr:rowOff>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12723,7 +12723,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="3238560"/>
-        <a:ext cx="4515840" cy="2740320"/>
+        <a:ext cx="4515480" cy="2739960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12742,9 +12742,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>302040</xdr:colOff>
+      <xdr:colOff>301680</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>73440</xdr:rowOff>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12753,7 +12753,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="6286680"/>
-        <a:ext cx="4515840" cy="2740320"/>
+        <a:ext cx="4515480" cy="2739960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">

--- a/Trabalho_2/dados/normal/quartoteste_helicenormal.xlsx
+++ b/Trabalho_2/dados/normal/quartoteste_helicenormal.xlsx
@@ -3952,11 +3952,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68167828"/>
-        <c:axId val="20343728"/>
+        <c:axId val="99270898"/>
+        <c:axId val="47212571"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68167828"/>
+        <c:axId val="99270898"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4022,7 +4022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20343728"/>
+        <c:crossAx val="47212571"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4030,7 +4030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20343728"/>
+        <c:axId val="47212571"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4106,7 +4106,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68167828"/>
+        <c:crossAx val="99270898"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7880,11 +7880,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="33888171"/>
-        <c:axId val="74185603"/>
+        <c:axId val="12627111"/>
+        <c:axId val="12214058"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33888171"/>
+        <c:axId val="12627111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7950,7 +7950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74185603"/>
+        <c:crossAx val="12214058"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7958,7 +7958,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74185603"/>
+        <c:axId val="12214058"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8034,7 +8034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33888171"/>
+        <c:crossAx val="12627111"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11808,11 +11808,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96582138"/>
-        <c:axId val="44841253"/>
+        <c:axId val="73403898"/>
+        <c:axId val="8734214"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96582138"/>
+        <c:axId val="73403898"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11878,7 +11878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44841253"/>
+        <c:crossAx val="8734214"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11886,7 +11886,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44841253"/>
+        <c:axId val="8734214"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11962,7 +11962,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96582138"/>
+        <c:crossAx val="73403898"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12682,9 +12682,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>301680</xdr:colOff>
+      <xdr:colOff>301320</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12693,7 +12693,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="190440"/>
-        <a:ext cx="4515480" cy="2740320"/>
+        <a:ext cx="4515120" cy="2739960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12712,9 +12712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>301680</xdr:colOff>
+      <xdr:colOff>301320</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12723,7 +12723,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="3238560"/>
-        <a:ext cx="4515480" cy="2739960"/>
+        <a:ext cx="4515120" cy="2739600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12742,9 +12742,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>301680</xdr:colOff>
+      <xdr:colOff>301320</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12753,7 +12753,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="6286680"/>
-        <a:ext cx="4515480" cy="2739960"/>
+        <a:ext cx="4515120" cy="2739600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
